--- a/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
@@ -509,10 +509,10 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="E2">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -520,16 +520,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="E3">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,13 +540,13 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>63.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -577,10 +577,10 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>46.3</v>
+        <v>45.2</v>
       </c>
       <c r="E6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C8">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +750,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -761,10 +761,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C4">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
+        <v>82</v>
+      </c>
+      <c r="C2">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="D2">
         <v>81</v>
       </c>
-      <c r="C2">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="D2">
-        <v>80</v>
-      </c>
       <c r="E2">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="D3">
         <v>17</v>
       </c>
       <c r="E3">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
     </row>
   </sheetData>
